--- a/modules/trading/reports/export/daily_history.xlsx
+++ b/modules/trading/reports/export/daily_history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,6 +623,92 @@
       </c>
       <c r="M4" s="3" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>5067.5</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>154.73</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>25859.25</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>6975.5</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>78409</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>4814.4</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>154.78</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>25486.75</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>6936.5</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>77773</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>

--- a/modules/trading/reports/export/daily_history.xlsx
+++ b/modules/trading/reports/export/daily_history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,6 +711,178 @@
         <v>0.74</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>4938.3</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>155.88</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>25994.25</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>7022.5</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>78279</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>5070.3</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>156.71</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>25381.75</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>6949.75</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>75527</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>4883.6</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>156.83</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>24921.25</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>6875.75</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>69932</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>62.16</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>4969.3</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>157.08</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>24827.75</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>6883.75</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>68123</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/modules/trading/reports/export/daily_history.xlsx
+++ b/modules/trading/reports/export/daily_history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,6 +883,49 @@
         <v>0.74</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>5076</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>153.7</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>25367.25</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>6983.25</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>67765</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
